--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104610_W17.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104610_W17.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. PEREZ</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5991</v>
+        <v>4.9096</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8578</v>
+        <v>3.4294</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7414</v>
+        <v>1.4801</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1576</v>
+        <v>3.459</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.658</v>
+        <v>3.4064</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8157</v>
+        <v>0.0526</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0075</v>
+        <v>2.9515</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.8454</v>
+        <v>2.244</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8529</v>
+        <v>0.7075</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1502</v>
+        <v>0.5074</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1874</v>
+        <v>1.1623</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0372</v>
+        <v>-0.6549</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>5.0293</v>
+        <v>-0.7071</v>
       </c>
       <c r="T2" t="n">
-        <v>4.0921</v>
+        <v>-0.9271</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9372</v>
+        <v>0.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.2472</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2534</v>
+        <v>1.405</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>C. DUARTE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5081</v>
+        <v>3.8727</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3411</v>
+        <v>2.4563</v>
       </c>
       <c r="F3" t="n">
-        <v>1.167</v>
+        <v>1.4164</v>
       </c>
       <c r="G3" t="n">
-        <v>3.451</v>
+        <v>4.6436</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4083</v>
+        <v>1.3757</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0427</v>
+        <v>3.2679</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9704</v>
+        <v>4.4937</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2614</v>
+        <v>0.4579</v>
       </c>
       <c r="L3" t="n">
-        <v>0.709</v>
+        <v>4.0358</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4806</v>
+        <v>0.1498</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1469</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6663</v>
+        <v>-0.768</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1036</v>
+        <v>-0.4945</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0434</v>
+        <v>-0.8506</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0602</v>
+        <v>0.3561</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4141</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. DUARTE</t>
+          <t>A. DIAZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6072</v>
+        <v>2.7572</v>
       </c>
       <c r="E4" t="n">
-        <v>2.043</v>
+        <v>2.7475</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5642</v>
+        <v>0.0097</v>
       </c>
       <c r="G4" t="n">
-        <v>4.651</v>
+        <v>0.7176</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3751</v>
+        <v>0.7202</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2759</v>
+        <v>-0.0026</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5403</v>
+        <v>1.2576</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4809</v>
+        <v>0.7067</v>
       </c>
       <c r="L4" t="n">
-        <v>4.0594</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1107</v>
+        <v>-0.54</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8943</v>
+        <v>0.0135</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7835</v>
+        <v>-0.5535</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7755</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3217</v>
+        <v>0.0834</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5462</v>
+        <v>-0.1819</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.6342</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DIAZ</t>
+          <t>T. PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6823</v>
+        <v>2.5335</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0532</v>
+        <v>0.3522</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3709</v>
+        <v>2.1812</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6977</v>
+        <v>0.1629</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7083</v>
+        <v>-0.655</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0106</v>
+        <v>0.8179</v>
       </c>
       <c r="J5" t="n">
-        <v>1.267</v>
+        <v>-0.0142</v>
       </c>
       <c r="K5" t="n">
-        <v>0.71</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.8411</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5693</v>
+        <v>0.1771</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0017</v>
+        <v>0.2003</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5676</v>
+        <v>-0.0232</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5878</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1496</v>
+        <v>1.964</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6261</v>
+        <v>1.6232</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5235</v>
+        <v>0.3408</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>1.639</v>
+        <v>1.2472</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. DJEDOVIC</t>
+          <t>A. RUBIT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0808</v>
+        <v>0.9155</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7598</v>
+        <v>-0.6826</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.679</v>
+        <v>1.598</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3798</v>
+        <v>-2.159</v>
       </c>
       <c r="H6" t="n">
-        <v>2.059</v>
+        <v>-1.1344</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6793</v>
+        <v>-1.0247</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9672</v>
+        <v>-0.5685</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4475</v>
+        <v>-0.7174</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.1489</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5875</v>
+        <v>-1.5906</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6115</v>
+        <v>-0.4169</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.199</v>
+        <v>-1.1736</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8598</v>
+        <v>0.4795</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3266</v>
+        <v>0.1136</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1865</v>
+        <v>0.3659</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3856</v>
+        <v>0.7739</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.639</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0541</v>
+        <v>0.5203</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6439</v>
+        <v>0.4778</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4102</v>
+        <v>0.0425</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2659</v>
+        <v>-0.2733</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3868</v>
+        <v>1.3817</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6526</v>
+        <v>-1.6551</v>
       </c>
       <c r="J7" t="n">
-        <v>1.012</v>
+        <v>0.9706</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4679</v>
+        <v>1.4404</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4559</v>
+        <v>-0.4698</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2779</v>
+        <v>-1.2439</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.0587</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.388</v>
+        <v>-0.1381</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3266</v>
+        <v>-0.4441</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7146</v>
+        <v>0.306</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. RUBIT</t>
+          <t>N. DJEDOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8003</v>
+        <v>0.3285</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5546</v>
+        <v>1.3757</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3549</v>
+        <v>-1.0472</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1616</v>
+        <v>0.3891</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1327</v>
+        <v>2.0647</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0289</v>
+        <v>-1.6757</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5576</v>
+        <v>1.9476</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7069</v>
+        <v>1.4339</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1493</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6039</v>
+        <v>-1.5585</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4258</v>
+        <v>0.6308</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1781</v>
+        <v>-2.1893</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3759</v>
+        <v>0.0988</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2299</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1461</v>
+        <v>0.7798</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7712</v>
+        <v>-0.387</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7712</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8332</v>
+        <v>-0.4319</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9264</v>
+        <v>-0.1575</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.2745</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1119</v>
+        <v>-1.1229</v>
       </c>
       <c r="H9" t="n">
-        <v>0.117</v>
+        <v>0.1123</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2289</v>
+        <v>-1.2352</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0253</v>
+        <v>-1.0699</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3055</v>
+        <v>-0.3317</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7198</v>
+        <v>-0.7382</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0866</v>
+        <v>-0.053</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4224</v>
+        <v>0.444</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9747</v>
+        <v>-0.5563</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.113</v>
+        <v>-0.2861</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8617</v>
+        <v>-0.2702</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W9" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2109</v>
+        <v>-1.817</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8114</v>
+        <v>-3.593</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6005</v>
+        <v>1.776</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6711</v>
+        <v>-1.6694</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2135</v>
+        <v>0.218</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8846</v>
+        <v>-1.8875</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5462</v>
+        <v>-1.558</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1039</v>
+        <v>0.1034</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.6501</v>
+        <v>-1.6614</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1249</v>
+        <v>-0.1114</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3675</v>
+        <v>0.763</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2299</v>
+        <v>0.4689</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1376</v>
+        <v>0.294</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. SULEJMANOVIC</t>
+          <t>C. AUDIGE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5581</v>
+        <v>-3.4187</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4436</v>
+        <v>-2.4098</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1145</v>
+        <v>-1.0089</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.2262</v>
+        <v>-3.0561</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7286</v>
+        <v>-0.9452</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4976</v>
+        <v>-2.1109</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.0908</v>
+        <v>-0.247</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5554</v>
+        <v>0.1034</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5354</v>
+        <v>-0.3505</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1354</v>
+        <v>-2.8091</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1732</v>
+        <v>-1.0487</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-1.7604</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.0487</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6681</v>
+        <v>0.6374</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6472</v>
+        <v>0.3412</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0209</v>
+        <v>0.2962</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. AUDIGE</t>
+          <t>E. SULEJMANOVIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2194</v>
+        <v>-3.6516</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2194</v>
+        <v>-2.5723</v>
       </c>
       <c r="F12" t="n">
-        <v>-1</v>
+        <v>-1.0793</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.0595</v>
+        <v>-4.2356</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.951</v>
+        <v>-1.7344</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1085</v>
+        <v>-2.5012</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2374</v>
+        <v>-3.1041</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1039</v>
+        <v>-1.562</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3413</v>
+        <v>-1.542</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.8221</v>
+        <v>-1.1315</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0549</v>
+        <v>-0.1724</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7672</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0415</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.16</v>
+        <v>0.5841</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4869</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3269</v>
+        <v>0.0523</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.510299999999999</v>
+        <v>6.5181</v>
       </c>
       <c r="E13" t="n">
-        <v>1.743400000000001</v>
+        <v>1.423699999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>4.766999999999999</v>
+        <v>5.094000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.1591</v>
+        <v>-3.144099999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>4.797700000000001</v>
+        <v>4.81</v>
       </c>
       <c r="I13" t="n">
-        <v>-7.9567</v>
+        <v>-7.9545</v>
       </c>
       <c r="J13" t="n">
-        <v>5.307099999999999</v>
+        <v>5.059299999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>3.162300000000001</v>
+        <v>3.023299999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>2.1448</v>
+        <v>2.0359</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.466100000000001</v>
+        <v>-8.2037</v>
       </c>
       <c r="N13" t="n">
-        <v>1.6353</v>
+        <v>1.7866</v>
       </c>
       <c r="O13" t="n">
-        <v>-10.1013</v>
+        <v>-9.990300000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1341</v>
+        <v>1.1381</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.6101</v>
+        <v>-13.6578</v>
       </c>
       <c r="R13" t="n">
-        <v>14.7442</v>
+        <v>14.7962</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5252</v>
+        <v>2.5322</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0451999999999998</v>
+        <v>-0.02669999999999995</v>
       </c>
       <c r="U13" t="n">
-        <v>2.5706</v>
+        <v>2.559</v>
       </c>
       <c r="V13" t="n">
-        <v>6.0098</v>
+        <v>5.992</v>
       </c>
       <c r="W13" t="n">
-        <v>10.0914</v>
+        <v>10.0493</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.0816</v>
+        <v>-4.057399999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5442</v>
+        <v>5.743</v>
       </c>
       <c r="E14" t="n">
-        <v>6.3452</v>
+        <v>6.0294</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.2864</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7613</v>
+        <v>3.7188</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.6171</v>
+        <v>-2.641</v>
       </c>
       <c r="I14" t="n">
-        <v>6.3785</v>
+        <v>6.3598</v>
       </c>
       <c r="J14" t="n">
-        <v>4.9833</v>
+        <v>4.9034</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.3946</v>
+        <v>-2.4388</v>
       </c>
       <c r="L14" t="n">
-        <v>7.3779</v>
+        <v>7.3422</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.222</v>
+        <v>-1.1846</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2225</v>
+        <v>-0.2022</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9994</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4854</v>
+        <v>-0.2521</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2692</v>
+        <v>0.0366</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7546</v>
+        <v>-0.2887</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5659</v>
+        <v>2.7356</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3072</v>
+        <v>2.6203</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2587</v>
+        <v>0.1153</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0324</v>
+        <v>1.028</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0041</v>
+        <v>-1.0161</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0365</v>
+        <v>2.0441</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3908</v>
+        <v>1.3548</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6243</v>
+        <v>-0.656</v>
       </c>
       <c r="L15" t="n">
-        <v>2.0151</v>
+        <v>2.0108</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3584</v>
+        <v>-0.3268</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3798</v>
+        <v>-0.3601</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>2.494</v>
+        <v>0.6573</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8238</v>
+        <v>0.176</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6702</v>
+        <v>0.4813</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8159</v>
+        <v>2.5354</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3685</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4474</v>
+        <v>1.9462</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9201</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9334</v>
+        <v>0.9443</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0133</v>
+        <v>-0.0103</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7431</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9351</v>
+        <v>0.9308</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.192</v>
+        <v>-0.2015</v>
       </c>
       <c r="M16" t="n">
-        <v>0.177</v>
+        <v>0.2048</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0017</v>
+        <v>0.0135</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6009</v>
+        <v>0.3055</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5353</v>
+        <v>-0.2978</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1362</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. SANT-ROOS</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3644</v>
+        <v>1.5996</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7124</v>
+        <v>1.6344</v>
       </c>
       <c r="F17" t="n">
-        <v>0.652</v>
+        <v>-0.0348</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0727</v>
+        <v>-0.0367</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9984</v>
+        <v>-0.4835</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0711</v>
+        <v>0.4468</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0953</v>
+        <v>1.6361</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3676</v>
+        <v>0.2068</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4629</v>
+        <v>1.4292</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0225</v>
+        <v>-1.6728</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6308</v>
+        <v>-0.6904</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3918</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4258</v>
+        <v>-0.7294</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1785</v>
+        <v>-0.5464</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2474</v>
+        <v>-0.183</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7071</v>
+        <v>0.5447</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>H. SANT-ROOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3151</v>
+        <v>0.7517</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8283</v>
+        <v>0.3226</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5132</v>
+        <v>0.4291</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0547</v>
+        <v>1.0688</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-1.0049</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4478</v>
+        <v>2.0737</v>
       </c>
       <c r="J18" t="n">
-        <v>1.655</v>
+        <v>2.0709</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2078</v>
+        <v>-0.3867</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4472</v>
+        <v>2.4576</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7097</v>
+        <v>-1.0022</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7103</v>
+        <v>-0.6182</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9994</v>
+        <v>-0.384</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8147</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.9913</v>
+        <v>-0.1789</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3731</v>
+        <v>-0.1745</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6182</v>
+        <v>-0.0044</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5463</v>
+        <v>0.7025</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
@@ -1891,19 +1891,19 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0521</v>
+        <v>-0.0173</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0174</v>
+        <v>0.0524</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1918,10 +1918,10 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -1936,22 +1936,22 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0487</v>
+        <v>-0.0174</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.894</v>
+        <v>-1.5032</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8321</v>
+        <v>-1.6148</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0618</v>
+        <v>0.1117</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5483</v>
+        <v>2.5537</v>
       </c>
       <c r="H20" t="n">
-        <v>0.821</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7273</v>
+        <v>1.7295</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0573</v>
+        <v>2.0507</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9005</v>
+        <v>0.8963</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1568</v>
+        <v>1.1543</v>
       </c>
       <c r="M20" t="n">
-        <v>0.491</v>
+        <v>0.503</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8544</v>
+        <v>-0.4634</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4869</v>
+        <v>-0.251</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3675</v>
+        <v>-0.2124</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2050,64 +2050,64 @@
         <v>-2.9062</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2046</v>
+        <v>-1.1062</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7016</v>
+        <v>-1.7999</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6892</v>
+        <v>-0.6847</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3881</v>
+        <v>-0.3932</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3011</v>
+        <v>-0.2915</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0138</v>
+        <v>0.0003</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1354</v>
+        <v>-0.1486</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.703</v>
+        <v>-0.6851</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7821</v>
+        <v>-0.7921</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6079</v>
+        <v>-0.4904</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1742</v>
+        <v>-0.3017</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.7959</v>
+        <v>-2.7951</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0029</v>
+        <v>-3.836</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9629</v>
+        <v>-1.853</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0399</v>
+        <v>-1.983</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1544</v>
+        <v>-2.1451</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4965</v>
+        <v>-0.4887</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6579</v>
+        <v>-1.6564</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3369</v>
+        <v>-1.3442</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8176</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7292</v>
+        <v>-0.5819</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6261</v>
+        <v>-0.5089</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1031</v>
+        <v>-0.073</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1667</v>
+        <v>-4.9558</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.1677</v>
+        <v>-5.8755</v>
       </c>
       <c r="F23" t="n">
-        <v>1.001</v>
+        <v>0.9197</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.1058</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7331</v>
+        <v>1.7265</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8312</v>
+        <v>-1.8323</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0898</v>
+        <v>0.0458</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2948</v>
+        <v>1.2681</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.205</v>
+        <v>-1.2223</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1879</v>
+        <v>-0.1516</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4383</v>
+        <v>0.4584</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6263</v>
+        <v>-0.61</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3466</v>
+        <v>-0.1184</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5867</v>
+        <v>-0.2306</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2401</v>
+        <v>0.1121</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.094</v>
+        <v>-6.6651</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.0918</v>
+        <v>-5.7708</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0022</v>
+        <v>-0.8943</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3367</v>
+        <v>-3.3446</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.4357</v>
+        <v>-2.4355</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.901</v>
+        <v>-0.909</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.2255</v>
+        <v>-3.2435</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5381</v>
+        <v>-1.5448</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.6874</v>
+        <v>-1.6987</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8976</v>
+        <v>-0.8907</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8084</v>
+        <v>-0.3613</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5565</v>
+        <v>-0.2023</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2519</v>
+        <v>-0.159</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.510400000000002</v>
+        <v>-6.518299999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.767099999999999</v>
+        <v>-5.094099999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7431</v>
+        <v>-1.424</v>
       </c>
       <c r="G25" t="n">
-        <v>3.158999999999999</v>
+        <v>3.144300000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-4.797599999999999</v>
+        <v>-4.8101</v>
       </c>
       <c r="I25" t="n">
-        <v>7.956700000000001</v>
+        <v>7.954400000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>8.466000000000001</v>
+        <v>8.203599999999998</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.6352</v>
+        <v>-1.7867</v>
       </c>
       <c r="L25" t="n">
-        <v>10.1014</v>
+        <v>9.9902</v>
       </c>
       <c r="M25" t="n">
-        <v>-5.307099999999999</v>
+        <v>-5.059399999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>-3.1623</v>
+        <v>-3.0235</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.1448</v>
+        <v>-2.036</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.134099999999999</v>
+        <v>-1.138</v>
       </c>
       <c r="Q25" t="n">
-        <v>-14.7441</v>
+        <v>-14.7961</v>
       </c>
       <c r="R25" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.525399999999999</v>
+        <v>-2.5321</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.5706</v>
+        <v>-2.559</v>
       </c>
       <c r="U25" t="n">
-        <v>0.04530000000000034</v>
+        <v>0.02680000000000002</v>
       </c>
       <c r="V25" t="n">
-        <v>-6.009799999999999</v>
+        <v>-5.9922</v>
       </c>
       <c r="W25" t="n">
-        <v>4.0817</v>
+        <v>4.0573</v>
       </c>
       <c r="X25" t="n">
-        <v>-10.0913</v>
+        <v>-10.0495</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104610_W17.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104610_W17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-4.057399999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104610_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-10.0495</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
